--- a/outputs/table/table1_baseline_characteristics.xlsx
+++ b/outputs/table/table1_baseline_characteristics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Characteristic</t>
   </si>
@@ -73,16 +73,19 @@
     <t>— Philips</t>
   </si>
   <si>
+    <t>— Canon</t>
+  </si>
+  <si>
     <t>57.1 ± 12.1</t>
   </si>
   <si>
     <t>20–91</t>
   </si>
   <si>
-    <t>692 (64.1%)</t>
-  </si>
-  <si>
-    <t>387 (35.9%)</t>
+    <t>698 (64.2%)</t>
+  </si>
+  <si>
+    <t>390 (35.8%)</t>
   </si>
   <si>
     <t>162.2 ± 8.2</t>
@@ -94,19 +97,25 @@
     <t>23.5 ± 3.1</t>
   </si>
   <si>
-    <t>324 (30.0%)</t>
-  </si>
-  <si>
-    <t>202 (18.7%)</t>
-  </si>
-  <si>
-    <t>83 (7.7%)</t>
-  </si>
-  <si>
-    <t>560 (51.9%)</t>
-  </si>
-  <si>
-    <t>317 (29.4%)</t>
+    <t>329 (30.2%)</t>
+  </si>
+  <si>
+    <t>204 (18.8%)</t>
+  </si>
+  <si>
+    <t>83 (7.6%)</t>
+  </si>
+  <si>
+    <t>566 (52.0%)</t>
+  </si>
+  <si>
+    <t>318 (29.2%)</t>
+  </si>
+  <si>
+    <t>202 (18.6%)</t>
+  </si>
+  <si>
+    <t>2 (0.2%)</t>
   </si>
   <si>
     <t>59.5 ± 12.7</t>
@@ -115,10 +124,10 @@
     <t>20–90</t>
   </si>
   <si>
-    <t>497 (53.9%)</t>
-  </si>
-  <si>
-    <t>425 (46.1%)</t>
+    <t>498 (53.8%)</t>
+  </si>
+  <si>
+    <t>427 (46.2%)</t>
   </si>
   <si>
     <t>162.5 ± 8.6</t>
@@ -130,34 +139,37 @@
     <t>23.3 ± 3.4</t>
   </si>
   <si>
-    <t>424 (46.0%)</t>
-  </si>
-  <si>
-    <t>285 (30.9%)</t>
+    <t>425 (45.9%)</t>
+  </si>
+  <si>
+    <t>285 (30.8%)</t>
   </si>
   <si>
     <t>168 (18.2%)</t>
   </si>
   <si>
-    <t>568 (61.6%)</t>
-  </si>
-  <si>
-    <t>219 (23.8%)</t>
+    <t>568 (61.4%)</t>
+  </si>
+  <si>
+    <t>219 (23.7%)</t>
   </si>
   <si>
     <t>135 (14.6%)</t>
   </si>
   <si>
+    <t>3 (0.3%)</t>
+  </si>
+  <si>
     <t>&lt;0.001</t>
   </si>
   <si>
-    <t>0.401</t>
-  </si>
-  <si>
-    <t>0.873</t>
-  </si>
-  <si>
-    <t>0.383</t>
+    <t>0.414</t>
+  </si>
+  <si>
+    <t>0.843</t>
+  </si>
+  <si>
+    <t>0.353</t>
   </si>
 </sst>
 </file>
@@ -515,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -537,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -551,10 +563,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -562,7 +574,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -570,10 +582,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -581,10 +593,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -592,13 +604,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -606,13 +618,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -620,13 +632,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -634,13 +646,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -648,13 +660,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -662,13 +674,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -676,7 +688,7 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -684,10 +696,10 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -695,10 +707,10 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -706,10 +718,21 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/table/table1_baseline_characteristics.xlsx
+++ b/outputs/table/table1_baseline_characteristics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>Characteristic</t>
   </si>
@@ -28,6 +28,9 @@
     <t>p-value</t>
   </si>
   <si>
+    <t>Demographics</t>
+  </si>
+  <si>
     <t>Age, years, mean ± SD</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
     <t>— M</t>
   </si>
   <si>
+    <t>Anthropometry</t>
+  </si>
+  <si>
     <t>Height, cm, mean ± SD</t>
   </si>
   <si>
@@ -52,6 +58,9 @@
     <t>BMI, kg/m², mean ± SD</t>
   </si>
   <si>
+    <t>Comorbidities</t>
+  </si>
+  <si>
     <t>Hypertension, n (%)</t>
   </si>
   <si>
@@ -59,6 +68,9 @@
   </si>
   <si>
     <t>Chronic kidney disease, n (%)</t>
+  </si>
+  <si>
+    <t>Imaging</t>
   </si>
   <si>
     <t>CT scanner vendor, n (%)</t>
@@ -527,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -548,44 +560,38 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>48</v>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
+      <c r="D5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -593,10 +599,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -604,41 +610,29 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -646,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -660,35 +654,32 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>15</v>
       </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -696,10 +687,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -707,32 +701,70 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/table/table1_baseline_characteristics.xlsx
+++ b/outputs/table/table1_baseline_characteristics.xlsx
@@ -88,100 +88,100 @@
     <t>— Canon</t>
   </si>
   <si>
-    <t>57.1 ± 12.1</t>
+    <t>57.3 ± 12.1</t>
   </si>
   <si>
     <t>20–91</t>
   </si>
   <si>
-    <t>698 (64.2%)</t>
-  </si>
-  <si>
-    <t>390 (35.8%)</t>
-  </si>
-  <si>
-    <t>162.2 ± 8.2</t>
-  </si>
-  <si>
-    <t>61.9 ± 10.6</t>
-  </si>
-  <si>
-    <t>23.5 ± 3.1</t>
-  </si>
-  <si>
-    <t>329 (30.2%)</t>
-  </si>
-  <si>
-    <t>204 (18.8%)</t>
-  </si>
-  <si>
-    <t>83 (7.6%)</t>
-  </si>
-  <si>
-    <t>566 (52.0%)</t>
-  </si>
-  <si>
-    <t>318 (29.2%)</t>
-  </si>
-  <si>
-    <t>202 (18.6%)</t>
-  </si>
-  <si>
-    <t>2 (0.2%)</t>
-  </si>
-  <si>
-    <t>59.5 ± 12.7</t>
+    <t>784 (62.3%)</t>
+  </si>
+  <si>
+    <t>475 (37.7%)</t>
+  </si>
+  <si>
+    <t>162.8 ± 8.0</t>
+  </si>
+  <si>
+    <t>62.0 ± 10.1</t>
+  </si>
+  <si>
+    <t>23.3 ± 2.9</t>
+  </si>
+  <si>
+    <t>385 (30.6%)</t>
+  </si>
+  <si>
+    <t>232 (18.4%)</t>
+  </si>
+  <si>
+    <t>105 (8.3%)</t>
+  </si>
+  <si>
+    <t>688 (54.6%)</t>
+  </si>
+  <si>
+    <t>329 (26.1%)</t>
+  </si>
+  <si>
+    <t>236 (18.7%)</t>
+  </si>
+  <si>
+    <t>6 (0.5%)</t>
+  </si>
+  <si>
+    <t>59.7 ± 12.3</t>
   </si>
   <si>
     <t>20–90</t>
   </si>
   <si>
-    <t>498 (53.8%)</t>
-  </si>
-  <si>
-    <t>427 (46.2%)</t>
-  </si>
-  <si>
-    <t>162.5 ± 8.6</t>
-  </si>
-  <si>
-    <t>61.8 ± 11.4</t>
-  </si>
-  <si>
-    <t>23.3 ± 3.4</t>
-  </si>
-  <si>
-    <t>425 (45.9%)</t>
-  </si>
-  <si>
-    <t>285 (30.8%)</t>
-  </si>
-  <si>
-    <t>168 (18.2%)</t>
-  </si>
-  <si>
-    <t>568 (61.4%)</t>
-  </si>
-  <si>
-    <t>219 (23.7%)</t>
-  </si>
-  <si>
-    <t>135 (14.6%)</t>
-  </si>
-  <si>
-    <t>3 (0.3%)</t>
+    <t>576 (51.3%)</t>
+  </si>
+  <si>
+    <t>547 (48.7%)</t>
+  </si>
+  <si>
+    <t>163.7 ± 8.3</t>
+  </si>
+  <si>
+    <t>62.4 ± 10.1</t>
+  </si>
+  <si>
+    <t>23.2 ± 2.9</t>
+  </si>
+  <si>
+    <t>507 (45.1%)</t>
+  </si>
+  <si>
+    <t>335 (29.8%)</t>
+  </si>
+  <si>
+    <t>188 (16.7%)</t>
+  </si>
+  <si>
+    <t>654 (58.2%)</t>
+  </si>
+  <si>
+    <t>217 (19.3%)</t>
+  </si>
+  <si>
+    <t>228 (20.3%)</t>
+  </si>
+  <si>
+    <t>24 (2.1%)</t>
   </si>
   <si>
     <t>&lt;0.001</t>
   </si>
   <si>
-    <t>0.414</t>
-  </si>
-  <si>
-    <t>0.843</t>
-  </si>
-  <si>
-    <t>0.353</t>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.418</t>
+  </si>
+  <si>
+    <t>0.339</t>
   </si>
 </sst>
 </file>
